--- a/Test20251606.xlsx
+++ b/Test20251606.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/54e312b60f6066ea/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{C0116FB6-AF79-4B31-BDDF-F8F605B52EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{305C5D5A-A2DC-45F5-A1F0-5A3DB0825910}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{C0116FB6-AF79-4B31-BDDF-F8F605B52EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C5ECCFC-AEBA-4ECA-9EF8-4043CFD68725}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6C2F9C79-682A-483E-A29F-6CB5609D8DF1}"/>
   </bookViews>
@@ -106,14 +106,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{277A4ECD-26A2-490F-812E-36C8423C33A9}" name="Table1" displayName="Table1" ref="A1:B5" totalsRowShown="0">
-  <autoFilter ref="A1:B5" xr:uid="{277A4ECD-26A2-490F-812E-36C8423C33A9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{277A4ECD-26A2-490F-812E-36C8423C33A9}" name="Table1" displayName="Table1" ref="A1:B6" totalsRowShown="0">
+  <autoFilter ref="A1:B6" xr:uid="{277A4ECD-26A2-490F-812E-36C8423C33A9}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{7B157827-FC87-4C80-AFF1-3DC3088F6168}" name="C1"/>
     <tableColumn id="2" xr3:uid="{2E2983CC-9273-47CC-A7BE-AE4B53F4BE56}" name="C2" dataDxfId="0">
       <calculatedColumnFormula>Table1[[#This Row],[C1]]*10
      + 3
-          +2</calculatedColumnFormula>
+          +5</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -437,7 +437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{224E6213-5739-4464-A00E-2BF54313E316}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -455,8 +455,8 @@
       <c r="B2">
         <f>Table1[[#This Row],[C1]]*10
      + 3
-          +2</f>
-        <v>15</v>
+          +5</f>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -466,8 +466,8 @@
       <c r="B3">
         <f>Table1[[#This Row],[C1]]*10
      + 3
-          +2</f>
-        <v>25</v>
+          +5</f>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -477,19 +477,30 @@
       <c r="B4">
         <f>Table1[[#This Row],[C1]]*10
      + 3
-          +2</f>
-        <v>35</v>
+          +5</f>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5">
         <f>Table1[[#This Row],[C1]]*10
      + 3
-          +2</f>
-        <v>45</v>
+          +5</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <f>Table1[[#This Row],[C1]]*10
+     + 3
+          +5</f>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/Test20251606.xlsx
+++ b/Test20251606.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/54e312b60f6066ea/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{C0116FB6-AF79-4B31-BDDF-F8F605B52EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C5ECCFC-AEBA-4ECA-9EF8-4043CFD68725}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{C0116FB6-AF79-4B31-BDDF-F8F605B52EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B03BA7D7-9757-4CE1-A9E0-B21CDA379782}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6C2F9C79-682A-483E-A29F-6CB5609D8DF1}"/>
   </bookViews>
@@ -36,22 +36,31 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>C1</t>
   </si>
   <si>
     <t>C2</t>
   </si>
+  <si>
+    <t>C3</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -84,7 +93,10 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -106,15 +118,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{277A4ECD-26A2-490F-812E-36C8423C33A9}" name="Table1" displayName="Table1" ref="A1:B6" totalsRowShown="0">
-  <autoFilter ref="A1:B6" xr:uid="{277A4ECD-26A2-490F-812E-36C8423C33A9}"/>
-  <tableColumns count="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{277A4ECD-26A2-490F-812E-36C8423C33A9}" name="Table1" displayName="Table1" ref="A1:C7" totalsRowShown="0">
+  <autoFilter ref="A1:C7" xr:uid="{277A4ECD-26A2-490F-812E-36C8423C33A9}"/>
+  <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{7B157827-FC87-4C80-AFF1-3DC3088F6168}" name="C1"/>
     <tableColumn id="2" xr3:uid="{2E2983CC-9273-47CC-A7BE-AE4B53F4BE56}" name="C2" dataDxfId="0">
       <calculatedColumnFormula>Table1[[#This Row],[C1]]*10
      + 3
+-1
           +5</calculatedColumnFormula>
     </tableColumn>
+    <tableColumn id="3" xr3:uid="{DA41751D-4613-471F-BD13-38B117079FBC}" name="C3" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -437,73 +451,112 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{224E6213-5739-4464-A00E-2BF54313E316}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
         <f>Table1[[#This Row],[C1]]*10
      + 3
+-1
           +5</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="C2" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
         <f>Table1[[#This Row],[C1]]*10
      + 3
+-1
           +5</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="C3" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
         <f>Table1[[#This Row],[C1]]*10
      + 3
+-1
           +5</f>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="C4" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
         <f>Table1[[#This Row],[C1]]*10
      + 3
+-1
           +5</f>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="C5" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6">
         <f>Table1[[#This Row],[C1]]*10
      + 3
+-1
           +5</f>
-        <v>58</v>
+        <v>57</v>
+      </c>
+      <c r="C6" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <f>Table1[[#This Row],[C1]]*10
+     + 3
+-1
+          +5</f>
+        <v>67</v>
+      </c>
+      <c r="C7" s="1">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
